--- a/companies/dev-mini/Finance/FY2022 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2022 Financial Summary.xlsx
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>571131</v>
+        <v>444600</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>128965</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>82906</v>
+        <v>75850</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>73694</v>
+        <v>61120</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>64484</v>
+        <v>45190</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>921180</v>
+        <v>719560</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>259820</v>
+        <v>461440</v>
       </c>
     </row>
   </sheetData>

--- a/companies/dev-mini/Finance/FY2022 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2022 Financial Summary.xlsx
@@ -474,20 +474,20 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>270570</v>
+        <v>236892</v>
       </c>
       <c r="C4" s="3">
-        <v>267670</v>
+        <v>234353</v>
       </c>
       <c r="D4" s="3">
-        <v>298562</v>
+        <v>261400</v>
       </c>
       <c r="E4" s="3">
-        <v>344198</v>
+        <v>301355</v>
       </c>
       <c r="F4" s="4">
         <f>SUM(B4:E4)</f>
-        <v>1181000</v>
+        <v>1034000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>444600</v>
+        <v>547200</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>92800</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>75850</v>
+        <v>68110</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>61120</v>
+        <v>62680</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>45190</v>
+        <v>46350</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>719560</v>
+        <v>819540</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>461440</v>
+        <v>214460</v>
       </c>
     </row>
   </sheetData>
